--- a/app-templates/users-template.xlsx
+++ b/app-templates/users-template.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="in">Export!$A$6:$F$6</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>Danh sách người dùng</t>
   </si>
@@ -51,6 +54,66 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>First name</t>
+  </si>
+  <si>
+    <t>Last name</t>
+  </si>
+  <si>
+    <t>Full name</t>
+  </si>
+  <si>
+    <t>Time zone</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>minioadmin</t>
+  </si>
+  <si>
+    <t>Vũ</t>
+  </si>
+  <si>
+    <t>minioadmin Vũ</t>
+  </si>
+  <si>
+    <t>anhvhhe@gmail.com</t>
+  </si>
+  <si>
+    <t>Africa/Accra</t>
+  </si>
+  <si>
+    <t>sdfdgf</t>
+  </si>
+  <si>
+    <t>fsc</t>
+  </si>
+  <si>
+    <t>sdv</t>
+  </si>
+  <si>
+    <t>fsc sdv</t>
+  </si>
+  <si>
+    <t>sdgfd@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -63,7 +126,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -222,8 +285,14 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+      <color indexed="9"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -232,108 +301,108 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -422,8 +491,16 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="23"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -451,7 +528,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" rgb="5B9BD5"/>
       </bottom>
       <diagonal/>
     </border>
@@ -460,7 +537,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.499984740745262" rgb="5B9BD5"/>
       </bottom>
       <diagonal/>
     </border>
@@ -522,16 +599,24 @@
       <left/>
       <right/>
       <top style="thin">
-        <color theme="4"/>
+        <color theme="4" rgb="5B9BD5"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color indexed="23"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -679,7 +764,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -688,6 +773,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="10" xfId="0" applyFill="true" applyAlignment="true" applyBorder="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1222,12 +1310,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="13.3148148148148" customWidth="1"/>
-    <col min="2" max="5" width="8.43518518518519" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="13.3148148148148"/>
+    <col min="2" max="5" customWidth="true" width="8.43518518518519"/>
+    <col min="6" max="6" customWidth="true" width="9.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1264,27 +1352,36 @@
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>6</v>
+      <c r="G6" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s" s="2">
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="2:5">
+      <c r="A7" t="n" s="0">
+        <v>1.0</v>
+      </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -1294,6 +1391,67 @@
       </c>
       <c r="E7" t="s">
         <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
